--- a/tame_output/ON/bt/strategyON_20230727.xlsx
+++ b/tame_output/ON/bt/strategyON_20230727.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,16 +605,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -763,11 +763,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.9%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -916,11 +916,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.8%</t>
+          <t>456.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -1054,26 +1054,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>105.1%</t>
+          <t>105.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.9%</t>
         </is>
       </c>
     </row>
@@ -1217,16 +1217,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.5%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>141.6%</t>
+          <t>141.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,16 +1370,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-07-25</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>136.1%</t>
+          <t>136.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>18.0%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1670"/>
+  <dimension ref="A1:G1671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39920,7 +39920,7 @@
         <v>45132</v>
       </c>
       <c r="B1670" t="n">
-        <v>2.878911290069859</v>
+        <v>2.879213581299979</v>
       </c>
       <c r="C1670" t="n">
         <v>3.008212759175893</v>
@@ -39936,6 +39936,29 @@
       </c>
       <c r="G1670" t="n">
         <v>4.283146879936983</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" s="2" t="n">
+        <v>45133</v>
+      </c>
+      <c r="B1671" t="n">
+        <v>2.885238654138422</v>
+      </c>
+      <c r="C1671" t="n">
+        <v>3.014274190562314</v>
+      </c>
+      <c r="D1671" t="n">
+        <v>1.52373800282634</v>
+      </c>
+      <c r="E1671" t="n">
+        <v>3.623412967379104</v>
+      </c>
+      <c r="F1671" t="n">
+        <v>2.127786868257192</v>
+      </c>
+      <c r="G1671" t="n">
+        <v>4.290946311516631</v>
       </c>
     </row>
   </sheetData>
